--- a/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
@@ -627,7 +627,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -974,9 +974,8 @@
     <row r="17"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,18 +78,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -125,8 +113,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -146,11 +138,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,38 +178,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,13 +214,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -617,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -631,13 +612,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,276 +628,204 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Legal &amp; Risk – Risk &amp; resilience</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Climate leadership</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Reach and maintain high levels of climate-change resilience maturity</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Maturity assessment of the University’s preparedness for climate-related impacts and capability to respond, assessed across relevant organisational functions:
 o	Governance and strategy
@@ -929,67 +837,58 @@
 o	Financial planning and reporting.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 8a(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 8a(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will report the University's climate-change resilience maturity rating, key gaps and priority actions in the 2026 Sustainability Report (building on the Climate Change Preparedness Framework assessment reported in 2025).</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>8a(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>Review of University Risk 16 Climate Change was completed in Nov 2025, as part of the annual review cycle.
 The review identified a positive trend, showing improved levels of climate‑change preparedness, with work underway to complete the end‑of‑2025 assessment.</t>
         </is>
       </c>
-      <c r="K16" s="19" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>All University risks including Risk 16 Climate Change were presented to RMCC and ARC in Nov 25 for their oversight.
 There will be a risk presentation of Risk 16 Climate Change at RMCC Meeting 1 in Feb 2026.</t>
         </is>
       </c>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
     </row>
     <row r="17"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="P16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1029,7 +928,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1041,12 +940,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1054,77 +953,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1175,143 +1074,143 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Legal and Risk</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr"/>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Review of University Risk 16 Climate Change was completed in Nov 2025, as part of the annual review cycle.
 The review identified a positive trend, showing improved levels of climate‑change preparedness, with work underway to complete the end‑of‑2025 assessment.</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>All University risks including Risk 16 Climate Change were presented to RMCC and ARC in Nov 25 for their oversight.
 There will be a risk presentation of Risk 16 Climate Change at RMCC Meeting 1 in Feb 2026.</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Case studies demonstrating climate change preparedness</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Flood Emergency Response Plans (FERP) for Southbank - MCM has been completed, while MTC is still in progress.
 The FERP for Creswick has also been completed and is awaiting review by FM Global.
 Case study -  In 2025, UoM received approximately $229k in resilience credits from FM Global, which can be applied to climate‑related projects.</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>As part of the University’s ongoing commitment to strengthening preparedness for climate‑related events, these FERPs will be reviewed regularly by both UoM  and FM Global. Ongoing training and awareness are also essential to ensuring the effectiveness of these plans.</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1330,13 +1229,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1352,21 +1251,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -1391,24 +1275,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1424,24 +1292,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1457,47 +1309,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -1505,11 +1325,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/LandR - SR26 sustainability reporting request.xlsx
@@ -20,21 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -178,61 +170,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,32 +610,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -661,171 +641,174 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Legal &amp; Risk – Risk &amp; resilience</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="204" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Climate leadership</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Reach and maintain high levels of climate-change resilience maturity</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Maturity assessment of the University’s preparedness for climate-related impacts and capability to respond, assessed across relevant organisational functions:
 o	Governance and strategy
@@ -837,46 +820,46 @@
 o	Financial planning and reporting.</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 8a(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will report the University's climate-change resilience maturity rating, key gaps and priority actions in the 2026 Sustainability Report (building on the Climate Change Preparedness Framework assessment reported in 2025).</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>8a(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>Review of University Risk 16 Climate Change was completed in Nov 2025, as part of the annual review cycle.
 The review identified a positive trend, showing improved levels of climate‑change preparedness, with work underway to complete the end‑of‑2025 assessment.</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>All University risks including Risk 16 Climate Change were presented to RMCC and ARC in Nov 25 for their oversight.
 There will be a risk presentation of Risk 16 Climate Change at RMCC Meeting 1 in Feb 2026.</t>
         </is>
       </c>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
     </row>
     <row r="17"/>
   </sheetData>
@@ -920,110 +903,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1054,163 +1029,152 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Legal and Risk</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Legal and Risk</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>Review of University Risk 16 Climate Change was completed in Nov 2025, as part of the annual review cycle.
 The review identified a positive trend, showing improved levels of climate‑change preparedness, with work underway to complete the end‑of‑2025 assessment.</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>All University risks including Risk 16 Climate Change were presented to RMCC and ARC in Nov 25 for their oversight.
 There will be a risk presentation of Risk 16 Climate Change at RMCC Meeting 1 in Feb 2026.</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Case studies demonstrating climate change preparedness</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Flood Emergency Response Plans (FERP) for Southbank - MCM has been completed, while MTC is still in progress.
 The FERP for Creswick has also been completed and is awaiting review by FM Global.
 Case study -  In 2025, UoM received approximately $229k in resilience credits from FM Global, which can be applied to climate‑related projects.</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>As part of the University’s ongoing commitment to strengthening preparedness for climate‑related events, these FERPs will be reviewed regularly by both UoM  and FM Global. Ongoing training and awareness are also essential to ensuring the effectiveness of these plans.</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1229,10 +1193,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -1254,7 +1225,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -1276,7 +1247,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1293,7 +1264,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1310,35 +1281,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>
